--- a/Recursividad/PruebaDeEscritorioLongitudRecursiva.xlsx
+++ b/Recursividad/PruebaDeEscritorioLongitudRecursiva.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03d0db00f6fa0e77/Documentos/Informatica1/samuel/Informatica-1/Recursividad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{6568BFA6-C4FF-44BD-9EA3-CB47C0869EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B307AD4-2A91-4CE9-B714-FA43FCBF90B5}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{6568BFA6-C4FF-44BD-9EA3-CB47C0869EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8691A6B-6AB3-49B7-85A4-EB24FF0A966C}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="15225" xr2:uid="{2B75A477-A9CF-47B7-B745-DD82E9186679}"/>
+    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="15578" xr2:uid="{2B75A477-A9CF-47B7-B745-DD82E9186679}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t xml:space="preserve">Mensaje por pantalla </t>
   </si>
@@ -44,103 +44,64 @@
     <t>Llamado a funciones</t>
   </si>
   <si>
-    <t>LongitudRecursiva</t>
-  </si>
-  <si>
-    <t>cadena</t>
-  </si>
-  <si>
-    <t>Hola, mundo!</t>
-  </si>
-  <si>
-    <t>longitud_cadena()</t>
-  </si>
-  <si>
-    <t>longitud_cadena("Hola, mundo!")</t>
-  </si>
-  <si>
-    <t>cadena==""</t>
-  </si>
-  <si>
-    <t>Llamado a funcion</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
-    <t>longitud_cadena("ola, mundo!")</t>
-  </si>
-  <si>
-    <t>ola, mundo!</t>
-  </si>
-  <si>
-    <t>longitud_cadena("la, mundo!")</t>
-  </si>
-  <si>
-    <t>la, mundo!</t>
-  </si>
-  <si>
-    <t>a, mundo!</t>
-  </si>
-  <si>
-    <t>, mundo!</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> mundo!</t>
-  </si>
-  <si>
-    <t>mundo!</t>
-  </si>
-  <si>
-    <t>undo!</t>
-  </si>
-  <si>
-    <t>ndo!</t>
-  </si>
-  <si>
-    <t>do!</t>
-  </si>
-  <si>
-    <t>o!</t>
-  </si>
-  <si>
-    <t>!</t>
-  </si>
-  <si>
     <t>V</t>
   </si>
   <si>
-    <t>longitud_cadena("")</t>
-  </si>
-  <si>
-    <t>longitud_cadena("a, mundo!")</t>
-  </si>
-  <si>
-    <t>longitud_cadena(", mundo!")</t>
-  </si>
-  <si>
-    <t>longitud_cadena(" mundo!")</t>
-  </si>
-  <si>
-    <t>longitud_cadena("mundo!")</t>
-  </si>
-  <si>
-    <t>longitud_cadena("undo!")</t>
-  </si>
-  <si>
-    <t>longitud_cadena("ndo!")</t>
-  </si>
-  <si>
-    <t>longitud_cadena("do!")</t>
-  </si>
-  <si>
-    <t>longitud_cadena("o!")</t>
-  </si>
-  <si>
-    <t>longitud_cadena("!")</t>
+    <t>PotenciaRecursiva</t>
+  </si>
+  <si>
+    <t>numBase</t>
+  </si>
+  <si>
+    <t>numExponente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrese la base: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrese el exponente: </t>
+  </si>
+  <si>
+    <t>potencia(2,3)</t>
+  </si>
+  <si>
+    <t>2 elevado a la 3 es: 8</t>
+  </si>
+  <si>
+    <t>resultado</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>exponente</t>
+  </si>
+  <si>
+    <t>exponente==0</t>
+  </si>
+  <si>
+    <t>llamado a funcion</t>
+  </si>
+  <si>
+    <t>2*2</t>
+  </si>
+  <si>
+    <t>potencia(2,3-1)</t>
+  </si>
+  <si>
+    <t>potencia(2,2-1)</t>
+  </si>
+  <si>
+    <t>2*2*2</t>
+  </si>
+  <si>
+    <t>potencia(2,1-1)</t>
+  </si>
+  <si>
+    <t>2*2*2*1</t>
   </si>
 </sst>
 </file>
@@ -164,7 +125,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -359,11 +320,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -378,6 +354,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,6 +372,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -712,247 +695,162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8090FB75-1E15-460F-A013-7A93DF31DE48}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="10">
-        <v>12</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="D12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="11">
+        <v>2</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="12">
-        <v>12</v>
-      </c>
+      <c r="E13" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>